--- a/scripts/Nucleus_SITE.xlsx
+++ b/scripts/Nucleus_SITE.xlsx
@@ -18011,15 +18011,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -18027,30 +18019,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -59963,11 +59931,11 @@
   </sheetData>
   <autoFilter ref="A1:I1433" xr:uid="{BC528FF1-5A61-42F5-ADF4-C382791C9D98}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I1433">
-      <sortCondition sortBy="cellColor" ref="B1:B1433" dxfId="4"/>
+      <sortCondition sortBy="cellColor" ref="B1:B1433" dxfId="1"/>
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/scripts/Nucleus_SITE.xlsx
+++ b/scripts/Nucleus_SITE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/884f899eba661abe/Python/Nucleus/scripts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="41" documentId="11_99DF8131EBE17A690A60020EA857A4CBA019281C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8CD3441B-A2A3-419F-8562-275E4FB1D8C4}"/>
+  <xr:revisionPtr revIDLastSave="45" documentId="11_99DF8131EBE17A690A60020EA857A4CBA019281C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F960551-683E-4933-8AFD-DE45787FC7A1}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -59929,11 +59929,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I1433" xr:uid="{BC528FF1-5A61-42F5-ADF4-C382791C9D98}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I1433">
-      <sortCondition sortBy="cellColor" ref="B1:B1433" dxfId="1"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A1:I1433" xr:uid="{BC528FF1-5A61-42F5-ADF4-C382791C9D98}"/>
   <conditionalFormatting sqref="B1:B1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>

--- a/scripts/Nucleus_SITE.xlsx
+++ b/scripts/Nucleus_SITE.xlsx
@@ -18011,7 +18011,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="1">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -18019,14 +18019,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
     </dxf>

--- a/scripts/Nucleus_SITE.xlsx
+++ b/scripts/Nucleus_SITE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/884f899eba661abe/Python/Nucleus/scripts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="45" documentId="11_99DF8131EBE17A690A60020EA857A4CBA019281C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F960551-683E-4933-8AFD-DE45787FC7A1}"/>
+  <xr:revisionPtr revIDLastSave="47" documentId="11_99DF8131EBE17A690A60020EA857A4CBA019281C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{63C89109-4328-45E1-A30A-F578F3A58A2A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
